--- a/Participant_Balances_Report_Trident_Abstract_Printable.xlsx
+++ b/Participant_Balances_Report_Trident_Abstract_Printable.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Original Report" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'By Participant'!$A$1:$E$59</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'By Participant'!$A$1:$E$68</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'By Participant'!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Fund Summary'!$3:$3</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Original Report'!$1:$2</definedName>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="82">
   <si>
     <t xml:space="preserve">Participant Balances Report - Trident Abstract (09-20-26)</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t xml:space="preserve">Check vs. Original Report total (should be 0):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fund Color Key</t>
   </si>
   <si>
     <t xml:space="preserve">Fund Summary - Trident Abstract (09-20-26)</t>
@@ -277,14 +280,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="[$$]#,##0.00;\-[$$]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="[$$]#,##0.00;\-[$$]#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +356,19 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -373,7 +390,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,14 +405,140 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD7CCC8"/>
+        <bgColor rgb="FFCFD8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F8"/>
         <bgColor rgb="FFF0F4FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF176"/>
+        <bgColor rgb="FFDCE775"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCAAA4"/>
+        <bgColor rgb="FFA6A6A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB39DDB"/>
+        <bgColor rgb="FF9FA8DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFD8DC"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAED581"/>
+        <bgColor rgb="FF81C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+        <bgColor rgb="FFFFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDBDBD"/>
+        <bgColor rgb="FFBCAAA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8A80"/>
+        <bgColor rgb="FFF48FB1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF48FB1"/>
+        <bgColor rgb="FFFF8A80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE93D8"/>
+        <bgColor rgb="FFB39DDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE775"/>
+        <bgColor rgb="FFFFF176"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB74D"/>
+        <bgColor rgb="FFFF8A80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1BEE7"/>
+        <bgColor rgb="FFD7CCC8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFCFD8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB6AC"/>
+        <bgColor rgb="FF81C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90CAF9"/>
+        <bgColor rgb="FF80DEEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FA8DA"/>
+        <bgColor rgb="FFB39DDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80DEEA"/>
+        <bgColor rgb="FF90CAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81C784"/>
+        <bgColor rgb="FFAED581"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0B2"/>
+        <bgColor rgb="FFFFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFCFD8DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,7 +554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -456,6 +599,21 @@
       </top>
       <bottom style="medium">
         <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,7 +702,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="153">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -573,7 +731,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,51 +743,143 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -637,63 +891,255 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="17" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="19" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="21" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="20" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="22" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="23" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="24" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -705,7 +1151,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -713,7 +1163,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="24" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -721,67 +1255,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="27" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="27" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="27" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="27" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="27" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="26" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -801,51 +1331,51 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFDCE775"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFB39DDB"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFBDBDBD"/>
       <rgbColor rgb="FFA6A6A6"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF9FA8DA"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF0F4FA"/>
       <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFFF8A80"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFCFD8DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFCDD2"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF80DEEA"/>
+      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFC8E6C9"/>
+      <rgbColor rgb="FFFFF176"/>
+      <rgbColor rgb="FF90CAF9"/>
+      <rgbColor rgb="FFF48FB1"/>
+      <rgbColor rgb="FFCE93D8"/>
+      <rgbColor rgb="FFFFE0B2"/>
+      <rgbColor rgb="FFD7CCC8"/>
+      <rgbColor rgb="FF4DB6AC"/>
+      <rgbColor rgb="FFAED581"/>
+      <rgbColor rgb="FFFFB74D"/>
+      <rgbColor rgb="FFBCAAA4"/>
+      <rgbColor rgb="FFE1BEE7"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF979991"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF81C784"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -1037,7 +1567,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1081,28 +1611,28 @@
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>1283.97</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <f aca="false">SUM(D5:D5)</f>
         <v>1283.97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="8" t="n">
         <v>1.63</v>
       </c>
       <c r="E6" s="12" t="n">
@@ -1117,89 +1647,89 @@
       <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="14" t="n">
         <v>291.83668</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <f aca="false">SUM(D7:D7)</f>
         <v>291.83668</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>97614.09054</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">SUM(D8:D13)</f>
         <v>178110.40696</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="22" t="n">
         <v>17256.06531</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="24" t="n">
         <v>13307.68725</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="26" t="n">
         <v>15904.98546</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="28" t="n">
         <v>17055.2152</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="31" t="n">
         <v>16972.3632</v>
       </c>
-      <c r="E13" s="20"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
@@ -1208,28 +1738,28 @@
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="33" t="n">
         <v>532.0123</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <f aca="false">SUM(D14:D14)</f>
         <v>532.0123</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="35" t="n">
         <v>49487.2586</v>
       </c>
       <c r="E15" s="12" t="n">
@@ -1238,56 +1768,56 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="B16" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="39" t="n">
         <v>133490.898</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="40" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>767978.95679</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="43" t="n">
         <v>113825.85879</v>
       </c>
-      <c r="E17" s="27"/>
+      <c r="E17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="46" t="n">
         <v>520662.2</v>
       </c>
-      <c r="E18" s="30"/>
+      <c r="E18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="33" t="n">
         <v>1422238.43981</v>
       </c>
       <c r="E19" s="12" t="n">
@@ -1302,28 +1832,28 @@
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="33" t="n">
         <v>371297.41994</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <f aca="false">SUM(D20:D20)</f>
         <v>371297.41994</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="35" t="n">
         <v>35305.41014</v>
       </c>
       <c r="E21" s="12" t="n">
@@ -1338,28 +1868,28 @@
       <c r="B22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="14" t="n">
         <v>68333.24672</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <f aca="false">SUM(D22:D22)</f>
         <v>68333.24672</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="48" t="n">
         <v>10648.24488</v>
       </c>
       <c r="E23" s="12" t="n">
@@ -1374,28 +1904,28 @@
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="33" t="n">
         <v>798248.20951</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <f aca="false">SUM(D24:D24)</f>
         <v>798248.20951</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="8" t="n">
         <v>61706.2</v>
       </c>
       <c r="E25" s="12" t="n">
@@ -1410,28 +1940,28 @@
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="50" t="n">
         <v>134068.10886</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="9" t="n">
         <f aca="false">SUM(D26:D26)</f>
         <v>134068.10886</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="48" t="n">
         <v>20590.63048</v>
       </c>
       <c r="E27" s="12" t="n">
@@ -1446,28 +1976,28 @@
       <c r="B28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="14" t="n">
         <v>92092.34216</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="9" t="n">
         <f aca="false">SUM(D28:D28)</f>
         <v>92092.34216</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="52" t="n">
         <v>1823.89275</v>
       </c>
       <c r="E29" s="12" t="n">
@@ -1482,28 +2012,28 @@
       <c r="B30" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="33" t="n">
         <v>158925.97069</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="9" t="n">
         <f aca="false">SUM(D30:D30)</f>
         <v>158925.97069</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="33" t="n">
         <v>4225.53531</v>
       </c>
       <c r="E31" s="12" t="n">
@@ -1512,45 +2042,45 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="54" t="n">
         <v>4269.80652</v>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="40" t="n">
         <f aca="false">SUM(D32:D33)</f>
         <v>14935.70116</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31" t="s">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="32" t="n">
+      <c r="D33" s="56" t="n">
         <v>10665.89464</v>
       </c>
-      <c r="E33" s="30"/>
+      <c r="E33" s="44"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="48" t="n">
         <v>108163.4022</v>
       </c>
       <c r="E34" s="12" t="n">
@@ -1559,73 +2089,73 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="24" t="s">
+      <c r="B35" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="58" t="n">
         <v>69571.39629</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="40" t="n">
         <f aca="false">SUM(D35:D37)</f>
         <v>595347.89089</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="28" t="s">
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="60" t="n">
         <v>398061.47444</v>
       </c>
-      <c r="E36" s="27"/>
+      <c r="E36" s="41"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="31" t="s">
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="32" t="n">
+      <c r="D37" s="62" t="n">
         <v>127715.02016</v>
       </c>
-      <c r="E37" s="30"/>
+      <c r="E37" s="44"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="39" t="n">
         <v>30102.66315</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="19" t="n">
         <f aca="false">SUM(D38:D39)</f>
         <v>113928.87221</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="22" t="n">
+      <c r="D39" s="64" t="n">
         <v>83826.20906</v>
       </c>
-      <c r="E39" s="20"/>
+      <c r="E39" s="29"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
@@ -1634,28 +2164,28 @@
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="52" t="n">
         <v>55974.7098</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="9" t="n">
         <f aca="false">SUM(D40:D40)</f>
         <v>55974.7098</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="B41" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="66" t="n">
         <v>234827.80219</v>
       </c>
       <c r="E41" s="12" t="n">
@@ -1670,45 +2200,45 @@
       <c r="B42" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="48" t="n">
         <v>2538.03984</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="9" t="n">
         <f aca="false">SUM(D42:D42)</f>
         <v>2538.03984</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="68" t="n">
         <v>15371.93746</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="19" t="n">
         <f aca="false">SUM(D43:D44)</f>
         <v>76507.42348</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="21" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="22" t="n">
+      <c r="D44" s="70" t="n">
         <v>61135.48602</v>
       </c>
-      <c r="E44" s="20"/>
+      <c r="E44" s="29"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
@@ -1717,28 +2247,28 @@
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="48" t="n">
         <v>15041.56584</v>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="9" t="n">
         <f aca="false">SUM(D45:D45)</f>
         <v>15041.56584</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="72" t="n">
         <v>1323.5557</v>
       </c>
       <c r="E46" s="12" t="n">
@@ -1753,28 +2283,28 @@
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="74" t="n">
         <v>34485.0168</v>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="9" t="n">
         <f aca="false">SUM(D47:D47)</f>
         <v>34485.0168</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="76" t="n">
         <v>72395.22444</v>
       </c>
       <c r="E48" s="12" t="n">
@@ -1789,28 +2319,28 @@
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="74" t="n">
         <v>104055.43776</v>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E49" s="9" t="n">
         <f aca="false">SUM(D49:D49)</f>
         <v>104055.43776</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="76" t="n">
         <v>618877.08344</v>
       </c>
       <c r="E50" s="12" t="n">
@@ -1825,28 +2355,28 @@
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D51" s="48" t="n">
         <v>128703.87544</v>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="9" t="n">
         <f aca="false">SUM(D51:D51)</f>
         <v>128703.87544</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="10" t="s">
+      <c r="B52" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="33" t="n">
         <v>82624.37598</v>
       </c>
       <c r="E52" s="12" t="n">
@@ -1861,81 +2391,81 @@
       <c r="B53" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D53" s="52" t="n">
         <v>242714.097</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="9" t="n">
         <f aca="false">SUM(D53:D53)</f>
         <v>242714.097</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="14" t="s">
+      <c r="B54" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="78" t="n">
         <v>136438.80335</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="19" t="n">
         <f aca="false">SUM(D54:D57)</f>
         <v>178604.55311</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18" t="s">
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="19" t="n">
+      <c r="D55" s="80" t="n">
         <v>9717.4026</v>
       </c>
-      <c r="E55" s="17"/>
+      <c r="E55" s="20"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18" t="s">
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="D56" s="19" t="n">
+      <c r="D56" s="82" t="n">
         <v>12847.584</v>
       </c>
-      <c r="E56" s="17"/>
+      <c r="E56" s="20"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="21" t="s">
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="22" t="n">
+      <c r="D57" s="62" t="n">
         <v>19600.76316</v>
       </c>
-      <c r="E57" s="20"/>
+      <c r="E57" s="29"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="33" t="s">
+      <c r="A58" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="35" t="s">
+      <c r="B58" s="84"/>
+      <c r="C58" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="D58" s="36" t="n">
+      <c r="D58" s="86" t="n">
         <f aca="false">SUM(D5:D57)</f>
         <v>6858238.34986</v>
       </c>
-      <c r="E58" s="36" t="n">
+      <c r="E58" s="86" t="n">
         <f aca="false">SUM(E5:E57)</f>
         <v>6858238.34986</v>
       </c>
@@ -1944,12 +2474,124 @@
       <c r="A59" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E59" s="37" t="n">
+      <c r="E59" s="87" t="n">
         <f aca="false">ROUND(E58-'Original Report'!X41,2)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="88" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" s="89"/>
+      <c r="C62" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="91"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" s="92"/>
+      <c r="C63" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="94"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" s="95"/>
+      <c r="C64" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="97"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="98" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="98"/>
+      <c r="C65" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="100"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="101" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" s="101"/>
+      <c r="C66" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="103"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="104" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="104"/>
+      <c r="C67" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="106" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="106"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="107"/>
+      <c r="C68" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="109"/>
+    </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="D68:E68"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1976,393 +2618,393 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="39" t="s">
+      <c r="B3" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="C3" s="111" t="s">
         <v>76</v>
       </c>
+      <c r="D3" s="111" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="40" t="n">
+      <c r="B4" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A4)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="41" t="n">
+      <c r="C4" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A4,'By Participant'!$D$5:$D$57)</f>
         <v>231682.1994</v>
       </c>
-      <c r="D4" s="42" t="n">
+      <c r="D4" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C4/$C$25)</f>
         <v>0.0337815904874069</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A5)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A5,'By Participant'!$D$5:$D$57)</f>
         <v>86827.4616</v>
       </c>
-      <c r="D5" s="45" t="n">
+      <c r="D5" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C5/$C$25)</f>
         <v>0.0126603155461595</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A6)</f>
         <v>3</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A6,'By Participant'!$D$5:$D$57)</f>
         <v>160717.42556</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C6/$C$25)</f>
         <v>0.0234342140592534</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A7)</f>
         <v>2</v>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A7,'By Participant'!$D$5:$D$57)</f>
         <v>371266.60554</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C7/$C$25)</f>
         <v>0.0541343981647385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A8)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A8,'By Participant'!$D$5:$D$57)</f>
         <v>473823.6633</v>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D8" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C8/$C$25)</f>
         <v>0.0690882467375419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A9)</f>
         <v>8</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A9,'By Participant'!$D$5:$D$57)</f>
         <v>2853463.901</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C9/$C$25)</f>
         <v>0.416063682163839</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A10)</f>
         <v>2</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A10,'By Participant'!$D$5:$D$57)</f>
         <v>691272.30788</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C10/$C$25)</f>
         <v>0.10079444204416</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A11)</f>
         <v>8</v>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A11,'By Participant'!$D$5:$D$57)</f>
         <v>688017.03964</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C11/$C$25)</f>
         <v>0.10031979125573</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A12)</f>
         <v>1</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A12,'By Participant'!$D$5:$D$57)</f>
         <v>83826.20906</v>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D12" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C12/$C$25)</f>
         <v>0.0122227027968066</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A13)</f>
         <v>1</v>
       </c>
-      <c r="C13" s="44" t="n">
+      <c r="C13" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A13,'By Participant'!$D$5:$D$57)</f>
         <v>1323.5557</v>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C13/$C$25)</f>
         <v>0.000192987707991662</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="40" t="n">
+      <c r="B14" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A14)</f>
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C14" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A14,'By Participant'!$D$5:$D$57)</f>
         <v>138540.45456</v>
       </c>
-      <c r="D14" s="42" t="n">
+      <c r="D14" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C14/$C$25)</f>
         <v>0.0202005890569301</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A15)</f>
         <v>2</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A15,'By Participant'!$D$5:$D$57)</f>
         <v>84792.66874</v>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C15/$C$25)</f>
         <v>0.0123636223202611</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="40" t="n">
+      <c r="B16" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A16)</f>
         <v>1</v>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A16,'By Participant'!$D$5:$D$57)</f>
         <v>113825.85879</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D16" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C16/$C$25)</f>
         <v>0.0165969528883935</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="131" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A17)</f>
         <v>1</v>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A17,'By Participant'!$D$5:$D$57)</f>
         <v>12847.584</v>
       </c>
-      <c r="D17" s="45" t="n">
+      <c r="D17" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C17/$C$25)</f>
         <v>0.0018733067217272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A18)</f>
         <v>1</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A18,'By Participant'!$D$5:$D$57)</f>
         <v>13307.68725</v>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D18" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C18/$C$25)</f>
         <v>0.0019403943944689</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="43" t="n">
+      <c r="B19" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A19)</f>
         <v>2</v>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A19,'By Participant'!$D$5:$D$57)</f>
         <v>147315.78332</v>
       </c>
-      <c r="D19" s="45" t="n">
+      <c r="D19" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C19/$C$25)</f>
         <v>0.0214801200840457</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A20)</f>
         <v>2</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A20,'By Participant'!$D$5:$D$57)</f>
         <v>77040.47148</v>
       </c>
-      <c r="D20" s="42" t="n">
+      <c r="D20" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C20/$C$25)</f>
         <v>0.011233274136874</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A21)</f>
         <v>1</v>
       </c>
-      <c r="C21" s="44" t="n">
+      <c r="C21" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A21,'By Participant'!$D$5:$D$57)</f>
         <v>17055.2152</v>
       </c>
-      <c r="D21" s="45" t="n">
+      <c r="D21" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C21/$C$25)</f>
         <v>0.0024868215903211</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="40" t="n">
+      <c r="B22" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A22)</f>
         <v>1</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A22,'By Participant'!$D$5:$D$57)</f>
         <v>16972.3632</v>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C22/$C$25)</f>
         <v>0.00247474093698515</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="43" t="n">
+      <c r="B23" s="117" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A23)</f>
         <v>4</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="118" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A23,'By Participant'!$D$5:$D$57)</f>
         <v>583654</v>
       </c>
-      <c r="D23" s="45" t="n">
+      <c r="D23" s="119" t="n">
         <f aca="false">IF($C$25=0,0,C23/$C$25)</f>
         <v>0.0851026123949038</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="40" t="n">
+      <c r="B24" s="113" t="n">
         <f aca="false">COUNTIF('By Participant'!$C$5:$C$57,A24)</f>
         <v>1</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="114" t="n">
         <f aca="false">SUMIF('By Participant'!$C$5:$C$57,A24,'By Participant'!$D$5:$D$57)</f>
         <v>10665.89464</v>
       </c>
-      <c r="D24" s="42" t="n">
+      <c r="D24" s="115" t="n">
         <f aca="false">IF($C$25=0,0,C24/$C$25)</f>
         <v>0.00155519451146193</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="46" t="n">
+      <c r="A25" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="139" t="n">
         <f aca="false">SUM(B4:B24)</f>
         <v>53</v>
       </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="86" t="n">
         <f aca="false">SUM(C4:C24)</f>
         <v>6858238.34986</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="140" t="n">
         <f aca="false">SUM(D4:D24)</f>
         <v>1</v>
       </c>
@@ -2403,1491 +3045,1491 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48"/>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="A1" s="141"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="142"/>
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
     </row>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="50" t="s">
+      <c r="A2" s="143" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="144" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="49" t="s">
+      <c r="W2" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="52" t="s">
-        <v>80</v>
+      <c r="X2" s="145" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="55" t="n">
+      <c r="B3" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="147"/>
+      <c r="M3" s="147"/>
+      <c r="N3" s="147"/>
+      <c r="O3" s="147"/>
+      <c r="P3" s="147"/>
+      <c r="Q3" s="147"/>
+      <c r="R3" s="147"/>
+      <c r="S3" s="147"/>
+      <c r="T3" s="147"/>
+      <c r="U3" s="147"/>
+      <c r="V3" s="148" t="n">
         <v>1283.97</v>
       </c>
-      <c r="W3" s="56"/>
-      <c r="X3" s="57" t="n">
+      <c r="W3" s="149"/>
+      <c r="X3" s="150" t="n">
         <f aca="false">SUM(C3:W3)</f>
         <v>1283.97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="55" t="n">
+      <c r="B4" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
+      <c r="R4" s="147"/>
+      <c r="S4" s="147"/>
+      <c r="T4" s="147"/>
+      <c r="U4" s="147"/>
+      <c r="V4" s="148" t="n">
         <v>1.63</v>
       </c>
-      <c r="W4" s="56"/>
-      <c r="X4" s="57" t="n">
+      <c r="W4" s="149"/>
+      <c r="X4" s="150" t="n">
         <f aca="false">SUM(C4:W4)</f>
         <v>1.63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55" t="n">
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="148" t="n">
         <v>291.83668</v>
       </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="57" t="n">
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
+      <c r="R5" s="147"/>
+      <c r="S5" s="147"/>
+      <c r="T5" s="147"/>
+      <c r="U5" s="147"/>
+      <c r="V5" s="147"/>
+      <c r="W5" s="149"/>
+      <c r="X5" s="150" t="n">
         <f aca="false">SUM(C5:W5)</f>
         <v>291.83668</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="55" t="n">
+      <c r="B6" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="148" t="n">
         <v>97614.09054</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="148" t="n">
         <v>17256.06531</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="55" t="n">
+      <c r="E6" s="147"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
+      <c r="L6" s="147"/>
+      <c r="M6" s="147"/>
+      <c r="N6" s="147"/>
+      <c r="O6" s="147"/>
+      <c r="P6" s="147"/>
+      <c r="Q6" s="148" t="n">
         <v>13307.68725</v>
       </c>
-      <c r="R6" s="54"/>
-      <c r="S6" s="55" t="n">
+      <c r="R6" s="147"/>
+      <c r="S6" s="148" t="n">
         <v>15904.98546</v>
       </c>
-      <c r="T6" s="55" t="n">
+      <c r="T6" s="148" t="n">
         <v>17055.2152</v>
       </c>
-      <c r="U6" s="55" t="n">
+      <c r="U6" s="148" t="n">
         <v>16972.3632</v>
       </c>
-      <c r="V6" s="54"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="57" t="n">
+      <c r="V6" s="147"/>
+      <c r="W6" s="149"/>
+      <c r="X6" s="150" t="n">
         <f aca="false">SUM(C6:W6)</f>
         <v>178110.40696</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55" t="n">
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="148" t="n">
         <v>532.0123</v>
       </c>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="57" t="n">
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="149"/>
+      <c r="X7" s="150" t="n">
         <f aca="false">SUM(C7:W7)</f>
         <v>532.0123</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55" t="n">
+      <c r="B8" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="148" t="n">
         <v>49487.2586</v>
       </c>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="57" t="n">
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="149"/>
+      <c r="X8" s="150" t="n">
         <f aca="false">SUM(C8:W8)</f>
         <v>49487.2586</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="55" t="n">
+      <c r="B9" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="148" t="n">
         <v>133490.898</v>
       </c>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="55" t="n">
+      <c r="H9" s="147"/>
+      <c r="I9" s="147"/>
+      <c r="J9" s="147"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="148" t="n">
         <v>113825.85879</v>
       </c>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="55" t="n">
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="147"/>
+      <c r="U9" s="147"/>
+      <c r="V9" s="148" t="n">
         <v>520662.2</v>
       </c>
-      <c r="W9" s="56"/>
-      <c r="X9" s="57" t="n">
+      <c r="W9" s="149"/>
+      <c r="X9" s="150" t="n">
         <f aca="false">SUM(C9:W9)</f>
         <v>767978.95679</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55" t="n">
+      <c r="B10" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
+      <c r="H10" s="148" t="n">
         <v>1422238.43981</v>
       </c>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="57" t="n">
+      <c r="I10" s="147"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="147"/>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
+      <c r="U10" s="147"/>
+      <c r="V10" s="147"/>
+      <c r="W10" s="149"/>
+      <c r="X10" s="150" t="n">
         <f aca="false">SUM(C10:W10)</f>
         <v>1422238.43981</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55" t="n">
+      <c r="B11" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="148" t="n">
         <v>371297.41994</v>
       </c>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="57" t="n">
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="147"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="147"/>
+      <c r="U11" s="147"/>
+      <c r="V11" s="147"/>
+      <c r="W11" s="149"/>
+      <c r="X11" s="150" t="n">
         <f aca="false">SUM(C11:W11)</f>
         <v>371297.41994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="55" t="n">
+      <c r="B12" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="147"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="148" t="n">
         <v>35305.41014</v>
       </c>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="57" t="n">
+      <c r="O12" s="147"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="147"/>
+      <c r="R12" s="147"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="147"/>
+      <c r="V12" s="147"/>
+      <c r="W12" s="149"/>
+      <c r="X12" s="150" t="n">
         <f aca="false">SUM(C12:W12)</f>
         <v>35305.41014</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="146" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55" t="n">
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="148" t="n">
         <v>68333.24672</v>
       </c>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="57" t="n">
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="149"/>
+      <c r="X13" s="150" t="n">
         <f aca="false">SUM(C13:W13)</f>
         <v>68333.24672</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="55" t="n">
+      <c r="B14" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="147"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="148" t="n">
         <v>10648.24488</v>
       </c>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="54"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="57" t="n">
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="147"/>
+      <c r="U14" s="147"/>
+      <c r="V14" s="147"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="150" t="n">
         <f aca="false">SUM(C14:W14)</f>
         <v>10648.24488</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55" t="n">
+      <c r="B15" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="148" t="n">
         <v>798248.20951</v>
       </c>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="57" t="n">
+      <c r="I15" s="147"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="P15" s="147"/>
+      <c r="Q15" s="147"/>
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="147"/>
+      <c r="U15" s="147"/>
+      <c r="V15" s="147"/>
+      <c r="W15" s="149"/>
+      <c r="X15" s="150" t="n">
         <f aca="false">SUM(C15:W15)</f>
         <v>798248.20951</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="54"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="55" t="n">
+      <c r="B16" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="147"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="147"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="147"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="147"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="148" t="n">
         <v>61706.2</v>
       </c>
-      <c r="W16" s="56"/>
-      <c r="X16" s="57" t="n">
+      <c r="W16" s="149"/>
+      <c r="X16" s="150" t="n">
         <f aca="false">SUM(C16:W16)</f>
         <v>61706.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="55" t="n">
+      <c r="B17" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="148" t="n">
         <v>134068.10886</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="57" t="n">
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="147"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="147"/>
+      <c r="P17" s="147"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="147"/>
+      <c r="U17" s="147"/>
+      <c r="V17" s="147"/>
+      <c r="W17" s="149"/>
+      <c r="X17" s="150" t="n">
         <f aca="false">SUM(C17:W17)</f>
         <v>134068.10886</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="55" t="n">
+      <c r="B18" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="148" t="n">
         <v>20590.63048</v>
       </c>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="57" t="n">
+      <c r="K18" s="147"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="147"/>
+      <c r="N18" s="147"/>
+      <c r="O18" s="147"/>
+      <c r="P18" s="147"/>
+      <c r="Q18" s="147"/>
+      <c r="R18" s="147"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="147"/>
+      <c r="U18" s="147"/>
+      <c r="V18" s="147"/>
+      <c r="W18" s="149"/>
+      <c r="X18" s="150" t="n">
         <f aca="false">SUM(C18:W18)</f>
         <v>20590.63048</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="55" t="n">
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="148" t="n">
         <v>92092.34216</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="54"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="57" t="n">
+      <c r="F19" s="147"/>
+      <c r="G19" s="147"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="147"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="147"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="147"/>
+      <c r="N19" s="147"/>
+      <c r="O19" s="147"/>
+      <c r="P19" s="147"/>
+      <c r="Q19" s="147"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="147"/>
+      <c r="W19" s="149"/>
+      <c r="X19" s="150" t="n">
         <f aca="false">SUM(C19:W19)</f>
         <v>92092.34216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55" t="n">
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="147"/>
+      <c r="G20" s="148" t="n">
         <v>1823.89275</v>
       </c>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="57" t="n">
+      <c r="H20" s="147"/>
+      <c r="I20" s="147"/>
+      <c r="J20" s="147"/>
+      <c r="K20" s="147"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="147"/>
+      <c r="N20" s="147"/>
+      <c r="O20" s="147"/>
+      <c r="P20" s="147"/>
+      <c r="Q20" s="147"/>
+      <c r="R20" s="147"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="147"/>
+      <c r="U20" s="147"/>
+      <c r="V20" s="147"/>
+      <c r="W20" s="149"/>
+      <c r="X20" s="150" t="n">
         <f aca="false">SUM(C20:W20)</f>
         <v>1823.89275</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="146" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55" t="n">
+      <c r="B21" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="147"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="148" t="n">
         <v>158925.97069</v>
       </c>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="56"/>
-      <c r="X21" s="57" t="n">
+      <c r="I21" s="147"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="147"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="147"/>
+      <c r="N21" s="147"/>
+      <c r="O21" s="147"/>
+      <c r="P21" s="147"/>
+      <c r="Q21" s="147"/>
+      <c r="R21" s="147"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="147"/>
+      <c r="U21" s="147"/>
+      <c r="V21" s="147"/>
+      <c r="W21" s="149"/>
+      <c r="X21" s="150" t="n">
         <f aca="false">SUM(C21:W21)</f>
         <v>158925.97069</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="146" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="55" t="n">
+      <c r="B22" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="148" t="n">
         <v>4225.53531</v>
       </c>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="56"/>
-      <c r="X22" s="57" t="n">
+      <c r="I22" s="147"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="147"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="147"/>
+      <c r="N22" s="147"/>
+      <c r="O22" s="147"/>
+      <c r="P22" s="147"/>
+      <c r="Q22" s="147"/>
+      <c r="R22" s="147"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="147"/>
+      <c r="U22" s="147"/>
+      <c r="V22" s="147"/>
+      <c r="W22" s="149"/>
+      <c r="X22" s="150" t="n">
         <f aca="false">SUM(C22:W22)</f>
         <v>4225.53531</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="146" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="55" t="n">
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="147"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="148" t="n">
         <v>4269.80652</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54"/>
-      <c r="W23" s="57" t="n">
+      <c r="K23" s="147"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="147"/>
+      <c r="P23" s="147"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="147"/>
+      <c r="W23" s="150" t="n">
         <v>10665.89464</v>
       </c>
-      <c r="X23" s="57" t="n">
+      <c r="X23" s="150" t="n">
         <f aca="false">SUM(C23:W23)</f>
         <v>14935.70116</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55" t="n">
+      <c r="B24" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="147"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="148" t="n">
         <v>108163.4022</v>
       </c>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="56"/>
-      <c r="X24" s="57" t="n">
+      <c r="K24" s="147"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="147"/>
+      <c r="N24" s="147"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="147"/>
+      <c r="Q24" s="147"/>
+      <c r="R24" s="147"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="147"/>
+      <c r="U24" s="147"/>
+      <c r="V24" s="147"/>
+      <c r="W24" s="149"/>
+      <c r="X24" s="150" t="n">
         <f aca="false">SUM(C24:W24)</f>
         <v>108163.4022</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="146" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="55" t="n">
+      <c r="B25" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="147"/>
+      <c r="D25" s="148" t="n">
         <v>69571.39629</v>
       </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="55" t="n">
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="148" t="n">
         <v>398061.47444</v>
       </c>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="54"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="55" t="n">
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="147"/>
+      <c r="N25" s="147"/>
+      <c r="O25" s="147"/>
+      <c r="P25" s="147"/>
+      <c r="Q25" s="147"/>
+      <c r="R25" s="148" t="n">
         <v>127715.02016</v>
       </c>
-      <c r="S25" s="54"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="54"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="57" t="n">
+      <c r="S25" s="147"/>
+      <c r="T25" s="147"/>
+      <c r="U25" s="147"/>
+      <c r="V25" s="147"/>
+      <c r="W25" s="149"/>
+      <c r="X25" s="150" t="n">
         <f aca="false">SUM(C25:W25)</f>
         <v>595347.89089</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55" t="n">
+      <c r="B26" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="148" t="n">
         <v>30102.66315</v>
       </c>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="55" t="n">
+      <c r="H26" s="147"/>
+      <c r="I26" s="147"/>
+      <c r="J26" s="147"/>
+      <c r="K26" s="148" t="n">
         <v>83826.20906</v>
       </c>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="54"/>
-      <c r="S26" s="54"/>
-      <c r="T26" s="54"/>
-      <c r="U26" s="54"/>
-      <c r="V26" s="54"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="57" t="n">
+      <c r="L26" s="147"/>
+      <c r="M26" s="147"/>
+      <c r="N26" s="147"/>
+      <c r="O26" s="147"/>
+      <c r="P26" s="147"/>
+      <c r="Q26" s="147"/>
+      <c r="R26" s="147"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="147"/>
+      <c r="V26" s="147"/>
+      <c r="W26" s="149"/>
+      <c r="X26" s="150" t="n">
         <f aca="false">SUM(C26:W26)</f>
         <v>113928.87221</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="146" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="55" t="n">
+      <c r="B27" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="148" t="n">
         <v>55974.7098</v>
       </c>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="54"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="57" t="n">
+      <c r="H27" s="147"/>
+      <c r="I27" s="147"/>
+      <c r="J27" s="147"/>
+      <c r="K27" s="147"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="147"/>
+      <c r="N27" s="147"/>
+      <c r="O27" s="147"/>
+      <c r="P27" s="147"/>
+      <c r="Q27" s="147"/>
+      <c r="R27" s="147"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="147"/>
+      <c r="U27" s="147"/>
+      <c r="V27" s="147"/>
+      <c r="W27" s="149"/>
+      <c r="X27" s="150" t="n">
         <f aca="false">SUM(C27:W27)</f>
         <v>55974.7098</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55" t="n">
+      <c r="B28" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="148" t="n">
         <v>234827.80219</v>
       </c>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="54"/>
-      <c r="W28" s="56"/>
-      <c r="X28" s="57" t="n">
+      <c r="G28" s="147"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="147"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="147"/>
+      <c r="N28" s="147"/>
+      <c r="O28" s="147"/>
+      <c r="P28" s="147"/>
+      <c r="Q28" s="147"/>
+      <c r="R28" s="147"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="147"/>
+      <c r="U28" s="147"/>
+      <c r="V28" s="147"/>
+      <c r="W28" s="149"/>
+      <c r="X28" s="150" t="n">
         <f aca="false">SUM(C28:W28)</f>
         <v>234827.80219</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="55" t="n">
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="148" t="n">
         <v>2538.03984</v>
       </c>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="54"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="56"/>
-      <c r="X29" s="57" t="n">
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="147"/>
+      <c r="P29" s="147"/>
+      <c r="Q29" s="147"/>
+      <c r="R29" s="147"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="147"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="147"/>
+      <c r="W29" s="149"/>
+      <c r="X29" s="150" t="n">
         <f aca="false">SUM(C29:W29)</f>
         <v>2538.03984</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="55" t="n">
+      <c r="B30" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="148" t="n">
         <v>15371.93746</v>
       </c>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="54"/>
-      <c r="R30" s="54"/>
-      <c r="S30" s="55" t="n">
+      <c r="I30" s="147"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="147"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="147"/>
+      <c r="R30" s="147"/>
+      <c r="S30" s="148" t="n">
         <v>61135.48602</v>
       </c>
-      <c r="T30" s="54"/>
-      <c r="U30" s="54"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="57" t="n">
+      <c r="T30" s="147"/>
+      <c r="U30" s="147"/>
+      <c r="V30" s="147"/>
+      <c r="W30" s="149"/>
+      <c r="X30" s="150" t="n">
         <f aca="false">SUM(C30:W30)</f>
         <v>76507.42348</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="55" t="n">
+      <c r="B31" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="147"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="147"/>
+      <c r="I31" s="147"/>
+      <c r="J31" s="148" t="n">
         <v>15041.56584</v>
       </c>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="57" t="n">
+      <c r="K31" s="147"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="147"/>
+      <c r="N31" s="147"/>
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="147"/>
+      <c r="R31" s="147"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="147"/>
+      <c r="U31" s="147"/>
+      <c r="V31" s="147"/>
+      <c r="W31" s="149"/>
+      <c r="X31" s="150" t="n">
         <f aca="false">SUM(C31:W31)</f>
         <v>15041.56584</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="55" t="n">
+      <c r="B32" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="147"/>
+      <c r="D32" s="147"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="147"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="147"/>
+      <c r="L32" s="148" t="n">
         <v>1323.5557</v>
       </c>
-      <c r="M32" s="54"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="54"/>
-      <c r="R32" s="54"/>
-      <c r="S32" s="54"/>
-      <c r="T32" s="54"/>
-      <c r="U32" s="54"/>
-      <c r="V32" s="54"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="57" t="n">
+      <c r="M32" s="147"/>
+      <c r="N32" s="147"/>
+      <c r="O32" s="147"/>
+      <c r="P32" s="147"/>
+      <c r="Q32" s="147"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="147"/>
+      <c r="U32" s="147"/>
+      <c r="V32" s="147"/>
+      <c r="W32" s="149"/>
+      <c r="X32" s="150" t="n">
         <f aca="false">SUM(C32:W32)</f>
         <v>1323.5557</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="55" t="n">
+      <c r="B33" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="147"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
+      <c r="H33" s="147"/>
+      <c r="I33" s="147"/>
+      <c r="J33" s="147"/>
+      <c r="K33" s="147"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="148" t="n">
         <v>34485.0168</v>
       </c>
-      <c r="N33" s="54"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="57" t="n">
+      <c r="N33" s="147"/>
+      <c r="O33" s="147"/>
+      <c r="P33" s="147"/>
+      <c r="Q33" s="147"/>
+      <c r="R33" s="147"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="147"/>
+      <c r="V33" s="147"/>
+      <c r="W33" s="149"/>
+      <c r="X33" s="150" t="n">
         <f aca="false">SUM(C33:W33)</f>
         <v>34485.0168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="55" t="n">
+      <c r="B34" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="147"/>
+      <c r="I34" s="148" t="n">
         <v>72395.22444</v>
       </c>
-      <c r="J34" s="54"/>
-      <c r="K34" s="54"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="54"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="54"/>
-      <c r="Q34" s="54"/>
-      <c r="R34" s="54"/>
-      <c r="S34" s="54"/>
-      <c r="T34" s="54"/>
-      <c r="U34" s="54"/>
-      <c r="V34" s="54"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="57" t="n">
+      <c r="J34" s="147"/>
+      <c r="K34" s="147"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="147"/>
+      <c r="N34" s="147"/>
+      <c r="O34" s="147"/>
+      <c r="P34" s="147"/>
+      <c r="Q34" s="147"/>
+      <c r="R34" s="147"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="147"/>
+      <c r="U34" s="147"/>
+      <c r="V34" s="147"/>
+      <c r="W34" s="149"/>
+      <c r="X34" s="150" t="n">
         <f aca="false">SUM(C34:W34)</f>
         <v>72395.22444</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="146" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="55" t="n">
+      <c r="B35" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="147"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="147"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="147"/>
+      <c r="J35" s="147"/>
+      <c r="K35" s="147"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="148" t="n">
         <v>104055.43776</v>
       </c>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="57" t="n">
+      <c r="N35" s="147"/>
+      <c r="O35" s="147"/>
+      <c r="P35" s="147"/>
+      <c r="Q35" s="147"/>
+      <c r="R35" s="147"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="147"/>
+      <c r="U35" s="147"/>
+      <c r="V35" s="147"/>
+      <c r="W35" s="149"/>
+      <c r="X35" s="150" t="n">
         <f aca="false">SUM(C35:W35)</f>
         <v>104055.43776</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="146" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="55" t="n">
+      <c r="B36" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="147"/>
+      <c r="D36" s="147"/>
+      <c r="E36" s="147"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="147"/>
+      <c r="I36" s="148" t="n">
         <v>618877.08344</v>
       </c>
-      <c r="J36" s="54"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="54"/>
-      <c r="N36" s="54"/>
-      <c r="O36" s="54"/>
-      <c r="P36" s="54"/>
-      <c r="Q36" s="54"/>
-      <c r="R36" s="54"/>
-      <c r="S36" s="54"/>
-      <c r="T36" s="54"/>
-      <c r="U36" s="54"/>
-      <c r="V36" s="54"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="57" t="n">
+      <c r="J36" s="147"/>
+      <c r="K36" s="147"/>
+      <c r="L36" s="147"/>
+      <c r="M36" s="147"/>
+      <c r="N36" s="147"/>
+      <c r="O36" s="147"/>
+      <c r="P36" s="147"/>
+      <c r="Q36" s="147"/>
+      <c r="R36" s="147"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="147"/>
+      <c r="U36" s="147"/>
+      <c r="V36" s="147"/>
+      <c r="W36" s="149"/>
+      <c r="X36" s="150" t="n">
         <f aca="false">SUM(C36:W36)</f>
         <v>618877.08344</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="55" t="n">
+      <c r="B37" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="147"/>
+      <c r="D37" s="147"/>
+      <c r="E37" s="147"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="147"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="147"/>
+      <c r="J37" s="148" t="n">
         <v>128703.87544</v>
       </c>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="57" t="n">
+      <c r="K37" s="147"/>
+      <c r="L37" s="147"/>
+      <c r="M37" s="147"/>
+      <c r="N37" s="147"/>
+      <c r="O37" s="147"/>
+      <c r="P37" s="147"/>
+      <c r="Q37" s="147"/>
+      <c r="R37" s="147"/>
+      <c r="S37" s="147"/>
+      <c r="T37" s="147"/>
+      <c r="U37" s="147"/>
+      <c r="V37" s="147"/>
+      <c r="W37" s="149"/>
+      <c r="X37" s="150" t="n">
         <f aca="false">SUM(C37:W37)</f>
         <v>128703.87544</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="146" t="s">
         <v>66</v>
       </c>
-      <c r="B38" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="55" t="n">
+      <c r="B38" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="148" t="n">
         <v>82624.37598</v>
       </c>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="54"/>
-      <c r="M38" s="54"/>
-      <c r="N38" s="54"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="54"/>
-      <c r="Q38" s="54"/>
-      <c r="R38" s="54"/>
-      <c r="S38" s="54"/>
-      <c r="T38" s="54"/>
-      <c r="U38" s="54"/>
-      <c r="V38" s="54"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="57" t="n">
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+      <c r="P38" s="147"/>
+      <c r="Q38" s="147"/>
+      <c r="R38" s="147"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="147"/>
+      <c r="U38" s="147"/>
+      <c r="V38" s="147"/>
+      <c r="W38" s="149"/>
+      <c r="X38" s="150" t="n">
         <f aca="false">SUM(C38:W38)</f>
         <v>82624.37598</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="55" t="n">
+      <c r="B39" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="147"/>
+      <c r="D39" s="147"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="147"/>
+      <c r="G39" s="148" t="n">
         <v>242714.097</v>
       </c>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="54"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="54"/>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="57" t="n">
+      <c r="H39" s="147"/>
+      <c r="I39" s="147"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="147"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="147"/>
+      <c r="N39" s="147"/>
+      <c r="O39" s="147"/>
+      <c r="P39" s="147"/>
+      <c r="Q39" s="147"/>
+      <c r="R39" s="147"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="147"/>
+      <c r="U39" s="147"/>
+      <c r="V39" s="147"/>
+      <c r="W39" s="149"/>
+      <c r="X39" s="150" t="n">
         <f aca="false">SUM(C39:W39)</f>
         <v>242714.097</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="146" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="55" t="n">
+      <c r="B40" s="146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="147"/>
+      <c r="D40" s="147"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="148" t="n">
         <v>136438.80335</v>
       </c>
-      <c r="G40" s="55" t="n">
+      <c r="G40" s="148" t="n">
         <v>9717.4026</v>
       </c>
-      <c r="H40" s="54"/>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="54"/>
-      <c r="N40" s="54"/>
-      <c r="O40" s="54"/>
-      <c r="P40" s="55" t="n">
+      <c r="H40" s="147"/>
+      <c r="I40" s="147"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="147"/>
+      <c r="L40" s="147"/>
+      <c r="M40" s="147"/>
+      <c r="N40" s="147"/>
+      <c r="O40" s="147"/>
+      <c r="P40" s="148" t="n">
         <v>12847.584</v>
       </c>
-      <c r="Q40" s="54"/>
-      <c r="R40" s="55" t="n">
+      <c r="Q40" s="147"/>
+      <c r="R40" s="148" t="n">
         <v>19600.76316</v>
       </c>
-      <c r="S40" s="54"/>
-      <c r="T40" s="54"/>
-      <c r="U40" s="54"/>
-      <c r="V40" s="54"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="57" t="n">
+      <c r="S40" s="147"/>
+      <c r="T40" s="147"/>
+      <c r="U40" s="147"/>
+      <c r="V40" s="147"/>
+      <c r="W40" s="149"/>
+      <c r="X40" s="150" t="n">
         <f aca="false">SUM(C40:W40)</f>
         <v>178604.55311</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="58"/>
-      <c r="V41" s="58"/>
-      <c r="W41" s="58"/>
-      <c r="X41" s="59" t="n">
+      <c r="A41" s="151"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="151"/>
+      <c r="H41" s="151"/>
+      <c r="I41" s="151"/>
+      <c r="J41" s="151"/>
+      <c r="K41" s="151"/>
+      <c r="L41" s="151"/>
+      <c r="M41" s="151"/>
+      <c r="N41" s="151"/>
+      <c r="O41" s="151"/>
+      <c r="P41" s="151"/>
+      <c r="Q41" s="151"/>
+      <c r="R41" s="151"/>
+      <c r="S41" s="151"/>
+      <c r="T41" s="151"/>
+      <c r="U41" s="151"/>
+      <c r="V41" s="151"/>
+      <c r="W41" s="151"/>
+      <c r="X41" s="152" t="n">
         <f aca="false">SUM(X3:X40)</f>
         <v>6858238.34986</v>
       </c>
